--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_admission_decision.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_admission_decision.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="detection_checks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decision'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decision'!$A$1:$M$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'detection_checks'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,20 +429,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,7 +460,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>protective_veto_validated</t>
+          <t>process_guard_validated</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -478,25 +480,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>family_l3_templates</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>node_validated_l3_templates</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>d7_total_rows</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>d7_fordqr_rows</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>protective_veto_rows</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>d7_report_rows</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>process_guard_rows</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>sensor_veto_rows</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>deployment_release</t>
         </is>
@@ -505,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-admission-v2.2</t>
+          <t>d7-admission-v2.3</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -521,26 +533,32 @@
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>39648</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>39648</v>
       </c>
-      <c r="I2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="b">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:M2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
